--- a/out/MLP_Base_repeat_4_000008.xlsx
+++ b/out/MLP_Base_repeat_4_000008.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.017459022789986</v>
+        <v>1.045076465039656</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>2.431863202161871</v>
+        <v>1.045076465039656</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>3.03186320216187</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>3.03186320216187</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>3.03186320216187</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.4174590227899861</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.4174590227899861</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.157166170459627</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.017459022789986</v>
+        <v>1.045076465039656</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.017459022789986</v>
+        <v>1.045076465039656</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.157166170459627</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.157166170459627</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>3.03186320216187</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.4174590227899861</v>
+        <v>-1.157166170459627</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.4174590227899861</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.017459022789986</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.157166170459627</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.017459022789986</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.017459022789986</v>
+        <v>1.045076465039656</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.017459022789986</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.017459022789986</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>3.03186320216187</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>3.03186320216187</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>3.03186320216187</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001691554525765823</v>
+        <v>-0.0001375234126630239</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.194327125711051</v>
+        <v>-0.1579879873436859</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.4174590227899861</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1944962811636276</v>
+        <v>-0.1581255107563488</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>3.03186320216187</v>
+        <v>1.045076465039656</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1944962811636276</v>
+        <v>-0.1581255107563488</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1944962811636276</v>
+        <v>-0.1581255107563488</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.017459022789986</v>
+        <v>1.045076465039656</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1944962811636276</v>
+        <v>-0.1581255107563488</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1944962811636276</v>
+        <v>-0.1581255107563488</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.017459022789986</v>
+        <v>1.045076465039656</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1944962811636276</v>
+        <v>-0.1581255107563488</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1944962811636276</v>
+        <v>-0.1581255107563488</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.017459022789986</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1944962811636276</v>
+        <v>-0.1581255107563488</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.017459022789986</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1944962811636276</v>
+        <v>-0.1581255107563488</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.017459022789986</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1944962811636276</v>
+        <v>-0.1581255107563488</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.017459022789986</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1944962811636276</v>
+        <v>-0.1581255107563488</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.017459022789986</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1944962811636276</v>
+        <v>-0.1581255107563488</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>3.03186320216187</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1944962811636276</v>
+        <v>-0.1581255107563488</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>3.03186320216187</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1946384352563177</v>
+        <v>-0.1582446333882272</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.5111534863075249</v>
+        <v>0.4283378551738887</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.4174590227899861</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.8286504852491278</v>
+        <v>0.6992535013266793</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03641957857970976</v>
+        <v>0.03051894566280475</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>3.03186320216187</v>
+        <v>1.045076465039656</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3895157688221172</v>
+        <v>0.3312665098784594</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.06386753190944916</v>
+        <v>0.05351983224341474</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>3.03186320216187</v>
+        <v>1.045076465039656</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4808192837446879</v>
+        <v>0.4077772275640904</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0775918203608528</v>
+        <v>0.06502058732025365</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.4174590227899861</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.57212905886361</v>
+        <v>0.4842932208569604</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.02053257473279303</v>
+        <v>0.01720591149552624</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5355036541393285</v>
+        <v>0.4536017728347986</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.01140767193122314</v>
+        <v>0.009558634174589331</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.431863202161871</v>
+        <v>1.045076465039656</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.537765949401522</v>
+        <v>0.4554967295306599</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02396727206053088</v>
+        <v>0.02008418567808663</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>3.03186320216187</v>
+        <v>1.045076465039656</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5743081143819687</v>
+        <v>0.4861184717419974</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.009413519576293846</v>
+        <v>0.007887566809657577</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>3.03186320216187</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5691461898919966</v>
+        <v>0.4817920525699325</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.006701547805553956</v>
+        <v>0.00561483867039475</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.4174590227899861</v>
+        <v>-1.157166170459627</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.57313356758849</v>
+        <v>0.4851326005783878</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002634740490555836</v>
+        <v>0.002207004762919474</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.017459022789986</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5716959137122088</v>
+        <v>0.4839270301451515</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001493253598333204</v>
+        <v>0.001251251731112717</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5720463259633398</v>
+        <v>0.4842198812095213</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0005657434461113168</v>
+        <v>0.0004729682768874608</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.571682994039183</v>
+        <v>0.4839147369205495</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002625333877501299</v>
+        <v>0.0002195959304568991</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5716418378905084</v>
+        <v>0.4838794453117223</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>9.349368591118489e-05</v>
+        <v>7.734718002410539e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5715649655683283</v>
+        <v>0.4838143553374407</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>2.409613085119914e-05</v>
+        <v>1.932627333460911e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5715195703011423</v>
+        <v>0.4837755822452032</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>9.309572549770066e-06</v>
+        <v>6.924643791475056e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5715145479618812</v>
+        <v>0.483770563629152</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>2.705352179376644e-06</v>
+        <v>1.677971888793091e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.017459022789986</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5715106753340242</v>
+        <v>0.4837665088363164</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>5.776969076452056e-07</v>
+        <v>-8.167273192660964e-07</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.157166170459627</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5715086071395206</v>
+        <v>0.4837638914328977</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-2.504786695239595e-06</v>
+        <v>-3.128590021429696e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.157166170459627</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5715030154795123</v>
+        <v>0.4837583741909079</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5714966914855044</v>
+        <v>0.4837520501969</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.571491323696926</v>
+        <v>0.4837466824083216</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.017459022789986</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5714913604454177</v>
+        <v>0.4837467191568133</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.017459022789986</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5714914706908932</v>
+        <v>0.4837468294022889</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.157166170459627</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5714915441878768</v>
+        <v>0.4837469028992725</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.017459022789986</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.571491727930336</v>
+        <v>0.4837470866417317</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>3.03186320216187</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5714932713669925</v>
+        <v>0.4837486300783881</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.4174590227899861</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5714947413066656</v>
+        <v>0.4837501000180612</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.4174590227899861</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5714959907553876</v>
+        <v>0.4837513494667832</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>3.03186320216187</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5714973504495849</v>
+        <v>0.4837527091609805</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>3.03186320216187</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5714951455400756</v>
+        <v>0.4837505042514713</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>3.03186320216187</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5714947413066656</v>
+        <v>0.4837501000180612</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>3.03186320216187</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5714938960913536</v>
+        <v>0.4837492548027493</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.4174590227899861</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.5714944473187309</v>
+        <v>0.4837498060301265</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.017459022789986</v>
+        <v>1.045076465039656</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5714941165823044</v>
+        <v>0.4837494752937001</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.017459022789986</v>
+        <v>1.045076465039656</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.57149382259437</v>
+        <v>0.4837491813057657</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5714938960913536</v>
+        <v>0.4837492548027493</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.017459022789986</v>
+        <v>1.045076465039656</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5714934551094517</v>
+        <v>0.4837488138208473</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.017459022789986</v>
+        <v>1.045076465039656</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5714933448639761</v>
+        <v>0.4837487035753718</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.017459022789986</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.5714933081154844</v>
+        <v>0.4837486668268801</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5714934551094517</v>
+        <v>0.4837488138208473</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>3.03186320216187</v>
+        <v>1.045076465039656</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.571492977379058</v>
+        <v>0.4837483360904536</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>3.03186320216187</v>
+        <v>1.045076465039656</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5714939328398453</v>
+        <v>0.483749291551241</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.4174590227899861</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5714938960913536</v>
+        <v>0.4837492548027493</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.4174590227899861</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5714935653549272</v>
+        <v>0.4837489240663229</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.017459022789986</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5714940063368291</v>
+        <v>0.4837493650482248</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5714933816124681</v>
+        <v>0.4837487403238637</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.5714931978700089</v>
+        <v>0.4837485565814045</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5714927936365989</v>
+        <v>0.4837481523479945</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5714919484212869</v>
+        <v>0.4837473071326825</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.017459022789986</v>
+        <v>1.045076465039656</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5714919116727952</v>
+        <v>0.4837472703841909</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5714920586667624</v>
+        <v>0.4837474173781581</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.017459022789986</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5714919851697788</v>
+        <v>0.4837473438811745</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>3.03186320216187</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5714920586667624</v>
+        <v>0.4837474173781581</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.4174590227899861</v>
+        <v>-1.157166170459627</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.5714920954152544</v>
+        <v>0.48374745412665</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>3.03186320216187</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5714919851697788</v>
+        <v>0.4837473438811745</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.4174590227899861</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5714924261516807</v>
+        <v>0.4837477848630764</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.4174590227899861</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5714923159062052</v>
+        <v>0.4837476746176009</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5714922791577133</v>
+        <v>0.483747637869109</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5714922056607297</v>
+        <v>0.4837475643721253</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.571492168912238</v>
+        <v>0.4837475276236336</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5714919484212869</v>
+        <v>0.4837473071326825</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5714918749243033</v>
+        <v>0.4837472336356989</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.5714918014273197</v>
+        <v>0.4837471601387153</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.017459022789986</v>
+        <v>-1.757166170459627</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5714918381758116</v>
+        <v>0.4837471968872072</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.017459022789986</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.571491727930336</v>
+        <v>0.4837470866417317</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>3.03186320216187</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.5714918381758116</v>
+        <v>0.4837471968872072</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.4174590227899861</v>
+        <v>1.645076465039656</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5714921321637461</v>
+        <v>0.4837474908751417</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP_Base_repeat_4_000008.xlsx
+++ b/out/MLP_Base_repeat_4_000008.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.017459022789986</v>
+        <v>0.6506528614989318</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>2.431863202161871</v>
+        <v>1.044861115779144</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>3.03186320216187</v>
+        <v>2.033277624339568</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>3.03186320216187</v>
+        <v>2.033277624339568</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>3.03186320216187</v>
+        <v>1.244861115779144</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.4174590227899861</v>
+        <v>0.4564446072187198</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.4174590227899861</v>
+        <v>-0.3319719013417047</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.017459022789986</v>
+        <v>0.4564446072187197</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>3.03186320216187</v>
+        <v>0.4564446072187197</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.4174590227899861</v>
+        <v>0.4564446072187197</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.4174590227899861</v>
+        <v>-0.3319719013417047</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.3319719013417047</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.017459022789986</v>
+        <v>0.4564446072187197</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>3.03186320216187</v>
+        <v>1.244861115779144</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>3.03186320216187</v>
+        <v>2.033277624339568</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>3.03186320216187</v>
+        <v>1.244861115779144</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001691554525765823</v>
+        <v>-0.0001283947753730463</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.194327125711051</v>
+        <v>-0.1475009364138571</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.4174590227899861</v>
+        <v>1.244861115779144</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1944962811636276</v>
+        <v>-0.1476293311892301</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>3.03186320216187</v>
+        <v>0.4564446072187197</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1944962811636276</v>
+        <v>-0.1476293311892301</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.017459022789986</v>
+        <v>0.4564446072187197</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1944962811636276</v>
+        <v>-0.1476293311892301</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1944962811636276</v>
+        <v>-0.1476293311892301</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1944962811636276</v>
+        <v>-0.1476293311892301</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1944962811636276</v>
+        <v>-0.1476293311892301</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1944962811636276</v>
+        <v>-0.1476293311892301</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1944962811636276</v>
+        <v>-0.1476293311892301</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1944962811636276</v>
+        <v>-0.1476293311892301</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1944962811636276</v>
+        <v>-0.1476293311892301</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1944962811636276</v>
+        <v>-0.1476293311892301</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.017459022789986</v>
+        <v>0.4564446072187197</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1944962811636276</v>
+        <v>-0.1476293311892301</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>3.03186320216187</v>
+        <v>1.244861115779144</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1944962811636276</v>
+        <v>-0.1476293311892301</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>3.03186320216187</v>
+        <v>1.244861115779144</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1946384352563177</v>
+        <v>-0.1477413340102106</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.5111534863075249</v>
+        <v>0.4027366366554846</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.4174590227899861</v>
+        <v>1.244861115779144</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.8286504852491278</v>
+        <v>0.6585052083908476</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03641957857970976</v>
+        <v>0.0286949008047615</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>3.03186320216187</v>
+        <v>1.244861115779144</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3895157688221172</v>
+        <v>0.3125123395747193</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.06386753190944916</v>
+        <v>0.05032107905300173</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>3.03186320216187</v>
+        <v>1.244861115779144</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4808192837446879</v>
+        <v>0.3844500207212337</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0775918203608528</v>
+        <v>0.06113385639058825</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.4174590227899861</v>
+        <v>0.4564446072187198</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.57212905886361</v>
+        <v>0.456392490520759</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.02053257473279303</v>
+        <v>0.01617755012178384</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.017459022789986</v>
+        <v>0.4564446072187198</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5355036541393285</v>
+        <v>0.4275353886378636</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.01140767193122314</v>
+        <v>0.008987046709344196</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.431863202161871</v>
+        <v>1.044861115779144</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.537765949401522</v>
+        <v>0.4293167910705614</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02396727206053088</v>
+        <v>0.01888381889557708</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>3.03186320216187</v>
+        <v>2.033277624339568</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5743081143819687</v>
+        <v>0.4581083708465272</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.009413519576293846</v>
+        <v>0.007415248096174925</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>3.03186320216187</v>
+        <v>1.244861115779144</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5691461898919966</v>
+        <v>0.454040229726912</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.006701547805553956</v>
+        <v>0.005280201254171121</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.4174590227899861</v>
+        <v>0.4564446072187198</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.57313356758849</v>
+        <v>0.4571810807811175</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002634740490555836</v>
+        <v>0.002075289316631451</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5716959137122088</v>
+        <v>0.4560473447978007</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001493253598333204</v>
+        <v>0.001175722485929253</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5720463259633398</v>
+        <v>0.4563222882521655</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0005657434461113168</v>
+        <v>0.0004447834153510995</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.571682994039183</v>
+        <v>0.4560351887043708</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002625333877501299</v>
+        <v>0.0002052834446924889</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5716418378905084</v>
+        <v>0.4560017539461811</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>9.349368591118489e-05</v>
+        <v>7.250322825798153e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5715649655683283</v>
+        <v>0.4559401986762691</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>2.409613085119914e-05</v>
+        <v>1.789531607963211e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5715195703011423</v>
+        <v>0.4559034122365159</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>9.309572549770066e-06</v>
+        <v>6.447658039816054e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5715145479618812</v>
+        <v>0.4558983943651069</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>2.705352179376644e-06</v>
+        <v>1.164281743501315e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5715106753340242</v>
+        <v>0.4558942668640281</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>5.776969076452056e-07</v>
+        <v>-8.167273192660964e-07</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5715086071395206</v>
+        <v>0.4558914657181504</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-2.504786695239595e-06</v>
+        <v>-3.128590021429696e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5715030154795123</v>
+        <v>0.455886021973144</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.413072433009741e-06</v>
+        <v>-4.70653621650487e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5714966914855044</v>
+        <v>0.4558800292397137</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.571491323696926</v>
+        <v>0.4558746614511353</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5714913604454177</v>
+        <v>0.455874698199627</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5714914706908932</v>
+        <v>0.4558748084451025</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5714915441878768</v>
+        <v>0.4558748819420861</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.017459022789986</v>
+        <v>0.4564446072187197</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.571491727930336</v>
+        <v>0.4558750656845453</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>3.03186320216187</v>
+        <v>0.4564446072187197</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5714932713669925</v>
+        <v>0.4558766091212018</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.4174590227899861</v>
+        <v>0.4564446072187197</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5714947413066656</v>
+        <v>0.4558780790608749</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.4174590227899861</v>
+        <v>0.4564446072187198</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5714959907553876</v>
+        <v>0.4558793285095969</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>3.03186320216187</v>
+        <v>1.244861115779144</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5714973504495849</v>
+        <v>0.4558806882037942</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>3.03186320216187</v>
+        <v>2.033277624339568</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5714951455400756</v>
+        <v>0.4558784832942849</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>3.03186320216187</v>
+        <v>2.033277624339568</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5714947413066656</v>
+        <v>0.4558780790608749</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>3.03186320216187</v>
+        <v>1.244861115779144</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5714938960913536</v>
+        <v>0.4558772338455629</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.4174590227899861</v>
+        <v>0.4564446072187197</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.5714944473187309</v>
+        <v>0.4558777850729402</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5714941165823044</v>
+        <v>0.4558774543365138</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.57149382259437</v>
+        <v>0.4558771603485793</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5714938960913536</v>
+        <v>0.4558772338455629</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5714934551094517</v>
+        <v>0.455876792863661</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5714933448639761</v>
+        <v>0.4558766826181854</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.5714933081154844</v>
+        <v>0.4558766458696937</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.017459022789986</v>
+        <v>0.2564446072187196</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5714934551094517</v>
+        <v>0.455876792863661</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>3.03186320216187</v>
+        <v>1.244861115779144</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.571492977379058</v>
+        <v>0.4558763151332673</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>3.03186320216187</v>
+        <v>1.244861115779144</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5714939328398453</v>
+        <v>0.4558772705940546</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.4174590227899861</v>
+        <v>0.4564446072187197</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5714938960913536</v>
+        <v>0.4558772338455629</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.4174590227899861</v>
+        <v>-0.3319719013417047</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5714935653549272</v>
+        <v>0.4558769031091365</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5714940063368291</v>
+        <v>0.4558773440910385</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5714933816124681</v>
+        <v>0.4558767193666773</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.5714931978700089</v>
+        <v>0.4558765356242181</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5714927936365989</v>
+        <v>0.4558761313908081</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5714919484212869</v>
+        <v>0.4558752861754962</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5714919116727952</v>
+        <v>0.4558752494270045</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5714920586667624</v>
+        <v>0.4558753964209717</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.017459022789986</v>
+        <v>0.4564446072187197</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5714919851697788</v>
+        <v>0.4558753229239881</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>3.03186320216187</v>
+        <v>0.4564446072187197</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5714920586667624</v>
+        <v>0.4558753964209717</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.4174590227899861</v>
+        <v>1.244861115779144</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.5714920954152544</v>
+        <v>0.4558754331694637</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>3.03186320216187</v>
+        <v>0.4564446072187197</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5714919851697788</v>
+        <v>0.4558753229239881</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.4174590227899861</v>
+        <v>0.4564446072187197</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5714924261516807</v>
+        <v>0.4558757639058901</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.4174590227899861</v>
+        <v>-0.3319719013417047</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5714923159062052</v>
+        <v>0.4558756536604145</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5714922791577133</v>
+        <v>0.4558756169119226</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5714922056607297</v>
+        <v>0.455875543414939</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.571492168912238</v>
+        <v>0.4558755066664473</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5714919484212869</v>
+        <v>0.4558752861754962</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5714918749243033</v>
+        <v>0.4558752126785126</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.5714918014273197</v>
+        <v>0.4558751391815289</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.017459022789986</v>
+        <v>-0.5319719013417048</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5714918381758116</v>
+        <v>0.4558751759300209</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.017459022789986</v>
+        <v>0.4564446072187197</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.571491727930336</v>
+        <v>0.4558750656845453</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>3.03186320216187</v>
+        <v>0.4564446072187197</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.5714918381758116</v>
+        <v>0.4558751759300209</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.4174590227899861</v>
+        <v>0.8506528614989318</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5714921321637461</v>
+        <v>0.4558754699179554</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP_Base_repeat_4_000008.xlsx
+++ b/out/MLP_Base_repeat_4_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.4526506066322327</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.6506528614989318</v>
+        <v>-0.3000000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.5015281438827515</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.044861115779144</v>
+        <v>-0.16</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.5770015716552734</v>
       </c>
       <c r="JB4" t="n">
-        <v>2.033277624339568</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.5925871729850769</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.033277624339568</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.5287671685218811</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.244861115779144</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.4760905504226685</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.4564446072187198</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.4684224128723145</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3319719013417047</v>
+        <v>0.16</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.4302722811698914</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.4466704726219177</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.4280090630054474</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.4472609460353851</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.4344179928302765</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>0.4344695508480072</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.4282599985599518</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>0.4894635379314423</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.4385408163070679</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.4082097411155701</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.4072244167327881</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>0.4090934991836548</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>0.4041202962398529</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.3957328200340271</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>0.4040999114513397</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.3983103930950165</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>0.4241676032543182</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.4060277342796326</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>0.4011572003364563</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>0.3937991857528687</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>0.4000853002071381</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.409639835357666</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>0.4280047416687012</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.4564446072187197</v>
+        <v>0.16</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.5510412454605103</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.4564446072187197</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.452347606420517</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.4564446072187197</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.4474938213825226</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3319719013417047</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>0.4390121102333069</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3319719013417047</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>0.4159590005874634</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.5319719013417048</v>
+        <v>0.3</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>0.4469313025474548</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.5319719013417048</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>0.409736841917038</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>0.4067851603031158</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.3</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>0.4687707722187042</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.16</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>0.4809120297431946</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.5319719013417048</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>0.4751890897750854</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.4564446072187197</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.5272569060325623</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.244861115779144</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.5907416939735413</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.033277624339568</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.5735911130905151</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.244861115779144</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001283947753730463</v>
+        <v>-0.0001228097873588558</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1475009364138571</v>
+        <v>-0.1410848578813508</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>0.4919456541538239</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.244861115779144</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1476293311892301</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.5542218089103699</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.4564446072187197</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1476293311892301</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>0.4639569520950317</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.4564446072187197</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1476293311892301</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>0.4888441264629364</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.16</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1476293311892301</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>0.455826997756958</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1476293311892301</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>0.4526351690292358</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.3</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1476293311892301</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.4479135274887085</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.3</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1476293311892301</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>0.4929527342319489</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.16</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1476293311892301</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>0.4691500663757324</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1476293311892301</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>0.4844306707382202</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.5319719013417048</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1476293311892301</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>0.4736246168613434</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.5319719013417048</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1476293311892301</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.4762648344039917</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.4564446072187197</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1476293311892301</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.5016244649887085</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.244861115779144</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1476293311892301</v>
+        <v>-0.1412076676687095</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.5534258484840393</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.244861115779144</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1477413340102106</v>
+        <v>-0.1413121770304537</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.4027366366554846</v>
+        <v>0.3757916070601471</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>0.4793412387371063</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.244861115779144</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.6585052083908476</v>
+        <v>0.6109930852152989</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0286949008047615</v>
+        <v>0.02677507310336224</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.5099911689758301</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.244861115779144</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3125123395747193</v>
+        <v>0.2881483723948053</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.05032107905300173</v>
+        <v>0.04695448371026761</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.5410574078559875</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.244861115779144</v>
+        <v>-0.16</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3844500207212337</v>
+        <v>0.3552732580513849</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.06113385639058825</v>
+        <v>0.05704384064092109</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.4814304113388062</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.4564446072187198</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.456392490520759</v>
+        <v>0.4224026120276426</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01617755012178384</v>
+        <v>0.01509539449132771</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.4407953023910522</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.4564446072187198</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4275353886378636</v>
+        <v>0.3954761061194129</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.008987046709344196</v>
+        <v>0.008385375693296686</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.5910756587982178</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.044861115779144</v>
+        <v>-0.16</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4293167910705614</v>
+        <v>0.3971379777487803</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01888381889557708</v>
+        <v>0.01762027491398807</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.5614907145500183</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.033277624339568</v>
+        <v>-0.3</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4581083708465272</v>
+        <v>0.424003070750671</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.007415248096174925</v>
+        <v>0.006918707910205981</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.5351382493972778</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.244861115779144</v>
+        <v>-0.3</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.454040229726912</v>
+        <v>0.4202068004091049</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005280201254171121</v>
+        <v>0.004926589551460587</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.4591324031352997</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.4564446072187198</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4571810807811175</v>
+        <v>0.4231371751362502</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002075289316631451</v>
+        <v>0.001935426523150355</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>0.4909715354442596</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4560473447978007</v>
+        <v>0.4220789592700268</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001175722485929253</v>
+        <v>0.001097110414411771</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.4426261484622955</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4563222882521655</v>
+        <v>0.422335264191529</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0004447834153510995</v>
+        <v>0.0004142498153533747</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.4399449825286865</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4560351887043708</v>
+        <v>0.4220669475197626</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002052834446924889</v>
+        <v>0.0001920719193714948</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.4171167314052582</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4560017539461811</v>
+        <v>0.4220353681178999</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>7.250322825798153e-05</v>
+        <v>6.685195119750372e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.4394848346710205</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4559401986762691</v>
+        <v>0.4219776426818173</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.789531607963211e-05</v>
+        <v>1.64643588246551e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>0.4556416571140289</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4559034122365159</v>
+        <v>0.421942842894549</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>6.447658039816054e-06</v>
+        <v>5.49368653649805e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.4475208222866058</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4558983943651069</v>
+        <v>0.4219378265124243</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>1.164281743501315e-06</v>
+        <v>6.505915982095382e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.4620373547077179</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4558942668640281</v>
+        <v>0.4219336630515936</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.4086292684078217</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4558914657181504</v>
+        <v>0.4219308619057159</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.427370697259903</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.455886021973144</v>
+        <v>0.4219254181607096</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.4450177550315857</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4558800292397137</v>
+        <v>0.4219194254272792</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>0.4576843082904816</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4558746614511353</v>
+        <v>0.4219140576387008</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.4692496955394745</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.455874698199627</v>
+        <v>0.4219140943871925</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.4603029191493988</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4558748084451025</v>
+        <v>0.421914204632668</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>0.4392673671245575</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.5319719013417048</v>
+        <v>0.16</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4558748819420861</v>
+        <v>0.4219142781296517</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>0.4828734993934631</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.4564446072187197</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4558750656845453</v>
+        <v>0.4219144618721108</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.5470597743988037</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.4564446072187197</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4558766091212018</v>
+        <v>0.4219160053087673</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.3543809950351715</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.4564446072187197</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4558780790608749</v>
+        <v>0.4219174752484404</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.3119083642959595</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.4564446072187198</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4558793285095969</v>
+        <v>0.4219187246971624</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.8717454075813293</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.244861115779144</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4558806882037942</v>
+        <v>0.4219200843913597</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.5812840461730957</v>
       </c>
       <c r="JB89" t="n">
-        <v>2.033277624339568</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4558784832942849</v>
+        <v>0.4219178794818504</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.6332957744598389</v>
       </c>
       <c r="JB90" t="n">
-        <v>2.033277624339568</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4558780790608749</v>
+        <v>0.4219174752484404</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.5840838551521301</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.244861115779144</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4558772338455629</v>
+        <v>0.4219166300331284</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>0.4856538772583008</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.4564446072187197</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4558777850729402</v>
+        <v>0.4219171812605057</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.453245997428894</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4558774543365138</v>
+        <v>0.4219168505240793</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>0.4743624329566956</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4558771603485793</v>
+        <v>0.4219165565361448</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.4541055262088776</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4558772338455629</v>
+        <v>0.4219166300331284</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>0.4284821748733521</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.455876792863661</v>
+        <v>0.4219161890512265</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.423242449760437</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4558766826181854</v>
+        <v>0.4219160788057509</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.4355409145355225</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4558766458696937</v>
+        <v>0.4219160420572592</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.4285867214202881</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.2564446072187196</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.455876792863661</v>
+        <v>0.4219161890512265</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.606593906879425</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.244861115779144</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4558763151332673</v>
+        <v>0.4219157113208328</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.6467034220695496</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.244861115779144</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4558772705940546</v>
+        <v>0.4219166667816201</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.4864897429943085</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.4564446072187197</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4558772338455629</v>
+        <v>0.4219166300331284</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>0.4669874608516693</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3319719013417047</v>
+        <v>0.16</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4558769031091365</v>
+        <v>0.421916299296702</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.4374529719352722</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4558773440910385</v>
+        <v>0.421916740278604</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.442550003528595</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4558767193666773</v>
+        <v>0.4219161155542429</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.4490508735179901</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4558765356242181</v>
+        <v>0.4219159318117837</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.4592735767364502</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4558761313908081</v>
+        <v>0.4219155275783737</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.4687853455543518</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4558752861754962</v>
+        <v>0.4219146823630617</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>0.4650417268276215</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4558752494270045</v>
+        <v>0.42191464561457</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.4672529399394989</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4558753964209717</v>
+        <v>0.4219147926085373</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.4486271440982819</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.4564446072187197</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4558753229239881</v>
+        <v>0.4219147191115536</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.5383211374282837</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.4564446072187197</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4558753964209717</v>
+        <v>0.4219147926085373</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.4462941884994507</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.244861115779144</v>
+        <v>0.16</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4558754331694637</v>
+        <v>0.4219148293570292</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.50642991065979</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.4564446072187197</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4558753229239881</v>
+        <v>0.4219147191115536</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.4250715374946594</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.4564446072187197</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4558757639058901</v>
+        <v>0.4219151600934556</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.4402031600475311</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3319719013417047</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4558756536604145</v>
+        <v>0.42191504984798</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.4080569446086884</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4558756169119226</v>
+        <v>0.4219150130994881</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>0.426432192325592</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.455875543414939</v>
+        <v>0.4219149396025045</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>0.4177968502044678</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4558755066664473</v>
+        <v>0.4219149028540128</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.4097775518894196</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4558752861754962</v>
+        <v>0.4219146823630617</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.4438174962997437</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4558752126785126</v>
+        <v>0.4219146088660781</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.4288159012794495</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4558751391815289</v>
+        <v>0.4219145353690945</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.4223562180995941</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.5319719013417048</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4558751759300209</v>
+        <v>0.4219145721175864</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.4542538523674011</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.4564446072187197</v>
+        <v>0.16</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4558750656845453</v>
+        <v>0.4219144618721108</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.5006858110427856</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.4564446072187197</v>
+        <v>0.5800000000000005</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4558751759300209</v>
+        <v>0.4219145721175864</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>0.4900408089160919</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.8506528614989318</v>
+        <v>1.000000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4558754699179554</v>
+        <v>0.4219148661055209</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP_Base_repeat_4_000008.xlsx
+++ b/out/MLP_Base_repeat_4_000008.xlsx
@@ -72494,7 +72494,7 @@
         <v>0.6332957744598389</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.9999999999999998</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC90" t="n">
         <v>0.4219174752484404</v>
@@ -73289,7 +73289,7 @@
         <v>0.5840838551521301</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.7199999999999999</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC91" t="n">
         <v>0.4219166300331284</v>
@@ -74084,7 +74084,7 @@
         <v>0.4856538772583008</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="JC92" t="n">
         <v>0.4219171812605057</v>
@@ -74879,7 +74879,7 @@
         <v>0.453245997428894</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC93" t="n">
         <v>0.4219168505240793</v>
@@ -75674,7 +75674,7 @@
         <v>0.4743624329566956</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC94" t="n">
         <v>0.4219165565361448</v>
@@ -80444,7 +80444,7 @@
         <v>0.606593906879425</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="JC100" t="n">
         <v>0.4219157113208328</v>
@@ -81239,7 +81239,7 @@
         <v>0.6467034220695496</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="JC101" t="n">
         <v>0.4219166667816201</v>
@@ -82034,7 +82034,7 @@
         <v>0.4864897429943085</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="JC102" t="n">
         <v>0.4219166300331284</v>
@@ -82829,7 +82829,7 @@
         <v>0.4669874608516693</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.16</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC103" t="n">
         <v>0.421916299296702</v>
@@ -83624,7 +83624,7 @@
         <v>0.4374529719352722</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC104" t="n">
         <v>0.421916740278604</v>
@@ -89189,7 +89189,7 @@
         <v>0.4486271440982819</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC111" t="n">
         <v>0.4219147191115536</v>
